--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1213-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1213-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19EB4380-C17E-43B8-B2B9-9320E3B396FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8A0E0FE-5272-4445-8ED3-3B9114FA2B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DF08DDD1-D3BB-4CA5-A2DF-8DADA5034E9C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{99C0937C-3DE8-455E-A81C-9ADB509C5696}"/>
   </bookViews>
   <sheets>
     <sheet name="1213-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1397,16 +1397,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36499449-3E0B-4534-9CF4-C0E1DB373EE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72182D8-C517-4A3E-BDFC-EDF06807A3FD}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="17" width="9.125" customWidth="1"/>
+    <col min="18" max="18" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +1434,7 @@
       <c r="Q1" s="26"/>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="Q2" s="28"/>
       <c r="R2" s="29"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1560,7 +1560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>2025</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>2024</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>2023</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>2022</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>2021</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>2020</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>2019</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>2018</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>2017</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>2016</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>2015</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="35">
         <v>2014</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>2013</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="35">
         <v>2012</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>2011</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="35">
         <v>2010</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>2009</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="35">
         <v>2008</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>2007</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="35">
         <v>2006</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>2005</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="35">
         <v>2004</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>2003</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="35">
         <v>2002</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>2001</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="35">
         <v>2000</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>1999</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="35">
         <v>1998</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>1997</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="35">
         <v>1996</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>1995</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="35">
         <v>1994</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>1993</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="35">
         <v>1990</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>1989</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="35">
         <v>1986</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>1984</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
         <v>25</v>
       </c>
